--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BASKONIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BASKONIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>107.5168</v>
+        <v>98.94750000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>88.71169999999999</v>
+        <v>84.7454</v>
       </c>
       <c r="F2" t="n">
-        <v>18.8052</v>
+        <v>14.202</v>
       </c>
       <c r="G2" t="n">
-        <v>66.9941</v>
+        <v>68.134</v>
       </c>
       <c r="H2" t="n">
-        <v>59.3038</v>
+        <v>32.2905</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6902</v>
+        <v>35.8432</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8216</v>
+        <v>77.4278</v>
       </c>
       <c r="K2" t="n">
-        <v>70.23400000000001</v>
+        <v>43.4251</v>
       </c>
       <c r="L2" t="n">
-        <v>8.5877</v>
+        <v>34.0025</v>
       </c>
       <c r="M2" t="n">
-        <v>-11.8277</v>
+        <v>-9.293699999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.9299</v>
+        <v>-11.1345</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8972000000000002</v>
+        <v>1.8405</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.071200000000001</v>
+        <v>-3.666999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-46.9007</v>
+        <v>-28.951</v>
       </c>
       <c r="R2" t="n">
-        <v>37.8297</v>
+        <v>25.2842</v>
       </c>
       <c r="S2" t="n">
-        <v>48.9726</v>
+        <v>7.5562</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7405</v>
+        <v>3.2927</v>
       </c>
       <c r="U2" t="n">
-        <v>8.2323</v>
+        <v>4.263500000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6217999999999997</v>
+        <v>26.9249</v>
       </c>
       <c r="W2" t="n">
-        <v>16.0512</v>
+        <v>32.9765</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.4295</v>
+        <v>-6.0515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>92.9158</v>
+        <v>85.2796</v>
       </c>
       <c r="E3" t="n">
-        <v>60.8709</v>
+        <v>67.5483</v>
       </c>
       <c r="F3" t="n">
-        <v>32.0447</v>
+        <v>17.7314</v>
       </c>
       <c r="G3" t="n">
-        <v>27.9398</v>
+        <v>66.9941</v>
       </c>
       <c r="H3" t="n">
-        <v>19.3454</v>
+        <v>59.3038</v>
       </c>
       <c r="I3" t="n">
-        <v>8.5944</v>
+        <v>7.6902</v>
       </c>
       <c r="J3" t="n">
-        <v>53.4786</v>
+        <v>78.8216</v>
       </c>
       <c r="K3" t="n">
-        <v>41.2012</v>
+        <v>70.23400000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>12.2781</v>
+        <v>8.5877</v>
       </c>
       <c r="M3" t="n">
-        <v>-25.5388</v>
+        <v>-11.8277</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.8554</v>
+        <v>-10.9299</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.6835</v>
+        <v>-0.8972000000000002</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.5623</v>
+        <v>-9.071200000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-53.8491</v>
+        <v>-46.9007</v>
       </c>
       <c r="R3" t="n">
-        <v>47.2871</v>
+        <v>37.8297</v>
       </c>
       <c r="S3" t="n">
-        <v>55.6716</v>
+        <v>26.735</v>
       </c>
       <c r="T3" t="n">
-        <v>31.9913</v>
+        <v>19.5767</v>
       </c>
       <c r="U3" t="n">
-        <v>23.6802</v>
+        <v>7.1583</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8667</v>
+        <v>0.6217999999999997</v>
       </c>
       <c r="W3" t="n">
-        <v>29.2502</v>
+        <v>16.0512</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.3837</v>
+        <v>-15.4295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>89.0853</v>
+        <v>73.6768</v>
       </c>
       <c r="E4" t="n">
-        <v>75.6574</v>
+        <v>48.3822</v>
       </c>
       <c r="F4" t="n">
-        <v>13.4276</v>
+        <v>25.2945</v>
       </c>
       <c r="G4" t="n">
-        <v>68.134</v>
+        <v>27.9398</v>
       </c>
       <c r="H4" t="n">
-        <v>32.2905</v>
+        <v>19.3454</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8432</v>
+        <v>8.5944</v>
       </c>
       <c r="J4" t="n">
-        <v>77.4278</v>
+        <v>53.4786</v>
       </c>
       <c r="K4" t="n">
-        <v>43.4251</v>
+        <v>41.2012</v>
       </c>
       <c r="L4" t="n">
-        <v>34.0025</v>
+        <v>12.2781</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.293699999999999</v>
+        <v>-25.5388</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.1345</v>
+        <v>-21.8554</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8405</v>
+        <v>-3.6835</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.666999999999999</v>
+        <v>-6.5623</v>
       </c>
       <c r="Q4" t="n">
-        <v>-28.951</v>
+        <v>-53.8491</v>
       </c>
       <c r="R4" t="n">
-        <v>25.2842</v>
+        <v>47.2871</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.3065</v>
+        <v>36.4323</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.7953</v>
+        <v>19.5026</v>
       </c>
       <c r="U4" t="n">
-        <v>3.4891</v>
+        <v>16.93</v>
       </c>
       <c r="V4" t="n">
-        <v>26.9249</v>
+        <v>15.8667</v>
       </c>
       <c r="W4" t="n">
-        <v>32.9765</v>
+        <v>29.2502</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.0515</v>
+        <v>-13.3837</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>77.82129999999999</v>
+        <v>49.5458</v>
       </c>
       <c r="E5" t="n">
-        <v>49.1019</v>
+        <v>30.1443</v>
       </c>
       <c r="F5" t="n">
-        <v>28.7199</v>
+        <v>19.4015</v>
       </c>
       <c r="G5" t="n">
         <v>14.7973</v>
@@ -844,13 +844,13 @@
         <v>50.7612</v>
       </c>
       <c r="S5" t="n">
-        <v>65.6099</v>
+        <v>37.3349</v>
       </c>
       <c r="T5" t="n">
-        <v>40.7721</v>
+        <v>21.8149</v>
       </c>
       <c r="U5" t="n">
-        <v>24.8384</v>
+        <v>15.5199</v>
       </c>
       <c r="V5" t="n">
         <v>2.8176</v>
@@ -877,13 +877,13 @@
         <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>27.1992</v>
+        <v>34.4706</v>
       </c>
       <c r="E6" t="n">
-        <v>23.6155</v>
+        <v>28.2132</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5835</v>
+        <v>6.2576</v>
       </c>
       <c r="G6" t="n">
         <v>24.8241</v>
@@ -922,13 +922,13 @@
         <v>29.3371</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7948</v>
+        <v>13.0663</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7535</v>
+        <v>8.3512</v>
       </c>
       <c r="U6" t="n">
-        <v>2.0412</v>
+        <v>4.7154</v>
       </c>
       <c r="V6" t="n">
         <v>4.3007</v>
@@ -955,13 +955,13 @@
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>10.852</v>
+        <v>30.9884</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.739500000000002</v>
+        <v>11.3856</v>
       </c>
       <c r="F7" t="n">
-        <v>12.5915</v>
+        <v>19.6027</v>
       </c>
       <c r="G7" t="n">
         <v>34.7848</v>
@@ -1000,13 +1000,13 @@
         <v>50.7611</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.391</v>
+        <v>16.7455</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7324</v>
+        <v>11.3928</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6585</v>
+        <v>5.3526</v>
       </c>
       <c r="V7" t="n">
         <v>7.6372</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9295</v>
+        <v>14.0054</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2532</v>
+        <v>10.8745</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.323700000000001</v>
+        <v>3.131</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0583999999999999</v>
+        <v>8.1952</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9760000000000002</v>
+        <v>6.3598</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9173</v>
+        <v>1.8357</v>
       </c>
       <c r="J8" t="n">
-        <v>3.103</v>
+        <v>37.3545</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4022</v>
+        <v>23.2198</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7009</v>
+        <v>14.1352</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1614</v>
+        <v>-29.1594</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3782</v>
+        <v>-16.8601</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7833</v>
+        <v>-12.2993</v>
       </c>
       <c r="P8" t="n">
-        <v>3.474</v>
+        <v>-16.4057</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.158</v>
+        <v>-57.9022</v>
       </c>
       <c r="R8" t="n">
-        <v>4.632</v>
+        <v>41.4972</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.05700000000000004</v>
+        <v>14.7159</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7946</v>
+        <v>7.0096</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8513999999999999</v>
+        <v>7.7066</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4293</v>
+        <v>7.500400000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5139</v>
+        <v>24.4128</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9432</v>
+        <v>-16.9132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8854</v>
+        <v>5.5998</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7569</v>
+        <v>5.5384</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8714000000000002</v>
+        <v>0.06150000000000011</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4381</v>
+        <v>-0.1511</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7544999999999999</v>
+        <v>-3.8459</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6836</v>
+        <v>3.6948</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6581</v>
+        <v>16.6386</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3558</v>
+        <v>8.2325</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3024</v>
+        <v>8.406699999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2199999999999999</v>
+        <v>-16.7893</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-12.0785</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3812</v>
+        <v>-4.711399999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>13.8965</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>-20.2656</v>
       </c>
       <c r="R9" t="n">
-        <v>0.965</v>
+        <v>34.1623</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4317</v>
+        <v>11.7667</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2061</v>
+        <v>7.9054</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2254</v>
+        <v>3.8619</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9843000000000002</v>
+        <v>-19.9125</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8576999999999999</v>
+        <v>1.2605</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.842</v>
+        <v>-21.1729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ALVES DE SOUZA SILVA</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2114</v>
+        <v>4.021</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3408</v>
+        <v>5.1139</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8706000000000002</v>
+        <v>-1.0932</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6017</v>
+        <v>-0.0583999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9177</v>
+        <v>-0.9760000000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.9173</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6001</v>
+        <v>3.103</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4373</v>
+        <v>1.4022</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1628</v>
+        <v>1.7009</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0017</v>
+        <v>-3.1614</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4804</v>
+        <v>-2.3782</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5212</v>
+        <v>-0.7833</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.544</v>
+        <v>3.474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>1.351</v>
+        <v>4.632</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6675</v>
+        <v>2.0345</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6358</v>
+        <v>1.6552</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03170000000000001</v>
+        <v>0.3792</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5139</v>
+        <v>-1.4293</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5139</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5139</v>
+        <v>-2.9432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VICENTE CARAZO</t>
+          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08309999999999999</v>
+        <v>1.9446</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0155</v>
+        <v>2.8163</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.8717</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4906</v>
+        <v>2.4381</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3571</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1335</v>
+        <v>1.6836</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1035</v>
+        <v>2.6581</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1035</v>
+        <v>1.3558</v>
       </c>
       <c r="L11" t="n">
+        <v>1.3024</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.2199999999999999</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.6012999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>0.3871</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.2536</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.1335</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.193</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3146</v>
+        <v>0.4908</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.119</v>
+        <v>0.2657</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1957</v>
+        <v>0.225</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2859</v>
+        <v>-0.9843000000000002</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8576999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2859</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. PRESA PEREZ</t>
+          <t>T. ALVES DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7089</v>
+        <v>0.7781</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1223</v>
+        <v>-0.3601</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5866</v>
+        <v>1.1382</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7776999999999999</v>
+        <v>3.6017</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6697</v>
+        <v>2.9177</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4473</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0562</v>
+        <v>2.6001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6831</v>
+        <v>2.4373</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6269</v>
+        <v>0.1628</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8338</v>
+        <v>1.0017</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0134</v>
+        <v>0.4804</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8204</v>
+        <v>0.5212</v>
       </c>
       <c r="P12" t="n">
-        <v>0.386</v>
+        <v>-1.544</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>0.386</v>
+        <v>1.351</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3173</v>
+        <v>0.2343</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1785</v>
+        <v>-0.06519999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1388</v>
+        <v>0.2994</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.5139</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>E. VICENTE CARAZO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9426</v>
+        <v>0.3905</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8733000000000005</v>
+        <v>0.1848</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.068900000000001</v>
+        <v>0.2057</v>
       </c>
       <c r="G13" t="n">
-        <v>8.1952</v>
+        <v>0.4906</v>
       </c>
       <c r="H13" t="n">
-        <v>6.3598</v>
+        <v>0.3571</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8357</v>
+        <v>0.1335</v>
       </c>
       <c r="J13" t="n">
-        <v>37.3545</v>
+        <v>0.1035</v>
       </c>
       <c r="K13" t="n">
-        <v>23.2198</v>
+        <v>0.1035</v>
       </c>
       <c r="L13" t="n">
-        <v>14.1352</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-29.1594</v>
+        <v>0.3871</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.8601</v>
+        <v>0.2536</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.2993</v>
+        <v>0.1335</v>
       </c>
       <c r="P13" t="n">
-        <v>-16.4057</v>
+        <v>0.193</v>
       </c>
       <c r="Q13" t="n">
-        <v>-57.9022</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>41.4972</v>
+        <v>0.193</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2322</v>
+        <v>-0.0073</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.7387</v>
+        <v>0.0813</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5064</v>
+        <v>-0.0886</v>
       </c>
       <c r="V13" t="n">
-        <v>7.500400000000001</v>
+        <v>-0.2859</v>
       </c>
       <c r="W13" t="n">
-        <v>24.4128</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.9132</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. ZHEKEL</t>
+          <t>I. PRESA PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.4662</v>
+        <v>-0.5622</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4533</v>
+        <v>0.078</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9871</v>
+        <v>-0.6402</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5042</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4045</v>
+        <v>0.6697</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9004</v>
+        <v>-1.4473</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8444</v>
+        <v>0.0562</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4502</v>
+        <v>0.6831</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2945</v>
+        <v>-0.6269</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3485</v>
+        <v>-0.8338</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9543999999999999</v>
+        <v>-0.0134</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3941</v>
+        <v>-0.8204</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.2811</v>
+        <v>0.386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5387</v>
+        <v>-0.1705</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4442</v>
+        <v>0.0218</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0945</v>
+        <v>-0.1924</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.528</v>
+        <v>-0.7079999999999992</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.5452</v>
+        <v>0.3384000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.982900000000001</v>
+        <v>-1.0465</v>
       </c>
       <c r="G15" t="n">
         <v>4.614100000000001</v>
@@ -1624,13 +1624,13 @@
         <v>7.9133</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.8637</v>
+        <v>-1.0436</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.6561</v>
+        <v>-0.7723</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2077</v>
+        <v>-0.2715</v>
       </c>
       <c r="V15" t="n">
         <v>-3.3137</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>N. ZHEKEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-12.8959</v>
+        <v>-3.6804</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.9302</v>
+        <v>-4.6943</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.9658</v>
+        <v>1.0138</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1511</v>
+        <v>0.5042</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8459</v>
+        <v>1.4045</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6948</v>
+        <v>-0.9004</v>
       </c>
       <c r="J16" t="n">
-        <v>16.6386</v>
+        <v>-0.8444</v>
       </c>
       <c r="K16" t="n">
-        <v>8.2325</v>
+        <v>0.4502</v>
       </c>
       <c r="L16" t="n">
-        <v>8.406699999999999</v>
+        <v>-1.2945</v>
       </c>
       <c r="M16" t="n">
-        <v>-16.7893</v>
+        <v>1.3485</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.0785</v>
+        <v>0.9543999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.711399999999999</v>
+        <v>0.3941</v>
       </c>
       <c r="P16" t="n">
-        <v>13.8965</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q16" t="n">
-        <v>-20.2656</v>
+        <v>-4.0532</v>
       </c>
       <c r="R16" t="n">
-        <v>34.1623</v>
+        <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.728800000000001</v>
+        <v>0.3245</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.563</v>
+        <v>0.2032</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.165999999999999</v>
+        <v>0.1213</v>
       </c>
       <c r="V16" t="n">
-        <v>-19.9125</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2605</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-21.1729</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-22.4488</v>
+        <v>-15.0822</v>
       </c>
       <c r="E17" t="n">
-        <v>-19.5654</v>
+        <v>-14.286</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8834</v>
+        <v>-0.7963000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-18.1416</v>
@@ -1780,13 +1780,13 @@
         <v>20.8446</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6433000000000001</v>
+        <v>6.7237</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7494999999999998</v>
+        <v>4.5302</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1062</v>
+        <v>2.1931</v>
       </c>
       <c r="V17" t="n">
         <v>-10.2265</v>
@@ -1813,13 +1813,13 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-25.4618</v>
+        <v>-20.6</v>
       </c>
       <c r="E18" t="n">
-        <v>-19.9036</v>
+        <v>-16.2452</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.558000000000001</v>
+        <v>-4.355000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-19.3063</v>
@@ -1858,13 +1858,13 @@
         <v>24.319</v>
       </c>
       <c r="S18" t="n">
-        <v>8.3866</v>
+        <v>13.2481</v>
       </c>
       <c r="T18" t="n">
-        <v>4.314</v>
+        <v>7.9724</v>
       </c>
       <c r="U18" t="n">
-        <v>4.0727</v>
+        <v>5.2756</v>
       </c>
       <c r="V18" t="n">
         <v>-13.9632</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>338.0476</v>
+        <v>359.0153</v>
       </c>
       <c r="E19" t="n">
-        <v>250.16</v>
+        <v>259.7777</v>
       </c>
       <c r="F19" t="n">
-        <v>87.88799999999998</v>
+        <v>99.23699999999998</v>
       </c>
       <c r="G19" t="n">
         <v>218.8829</v>
@@ -1924,10 +1924,10 @@
         <v>-138.0443</v>
       </c>
       <c r="O19" t="n">
-        <v>-49.66350000000001</v>
+        <v>-49.6635</v>
       </c>
       <c r="P19" t="n">
-        <v>-58.8673</v>
+        <v>-58.86729999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-437.1611</v>
@@ -1936,13 +1936,13 @@
         <v>378.2958</v>
       </c>
       <c r="S19" t="n">
-        <v>165.219</v>
+        <v>186.1873</v>
       </c>
       <c r="T19" t="n">
-        <v>103.1196</v>
+        <v>112.7382</v>
       </c>
       <c r="U19" t="n">
-        <v>62.1</v>
+        <v>73.44929999999999</v>
       </c>
       <c r="V19" t="n">
         <v>12.812</v>
